--- a/db/templates/contracts/contract_client_copy.xlsx
+++ b/db/templates/contracts/contract_client_copy.xlsx
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>匯款日期</t>
+          <t>預計繳款日</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C34" s="56" t="inlineStr">
         <is>
-          <t>訂金日期(訂單系統)</t>
+          <t>預計訂金繳款日(訂單系統)</t>
         </is>
       </c>
       <c r="D34" s="57" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="C35" s="56" t="inlineStr">
         <is>
-          <t>第一期款入帳日(訂單系統)</t>
+          <t>預計第一期繳款日(訂單系統)</t>
         </is>
       </c>
       <c r="D35" s="213" t="inlineStr">
         <is>
-          <t>服務款項匯款帳號：(代收付)</t>
+          <t>本案專屬虛擬帳號：</t>
         </is>
       </c>
       <c r="E35" s="213" t="n"/>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="C36" s="56" t="inlineStr">
         <is>
-          <t>第二期款入帳日(訂單系統)</t>
+          <t>預計第二期繳款日(訂單系統)</t>
         </is>
       </c>
       <c r="D36" s="62" t="inlineStr">
         <is>
-          <t>還不確定要給哪個帳號</t>
+          <t>案件專屬虛擬帳號(訂單系統)</t>
         </is>
       </c>
       <c r="E36" s="213" t="n"/>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C37" s="56" t="inlineStr">
         <is>
-          <t>訂金日期(訂單系統)</t>
+          <t>樓層費預計繳款日(訂單系統)</t>
         </is>
       </c>
       <c r="D37" s="213" t="inlineStr">

--- a/db/templates/contracts/contract_client_copy.xlsx
+++ b/db/templates/contracts/contract_client_copy.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客戶契約" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="客戶契約" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'客戶契約'!$A$1:$G$185</definedName>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="170" formatCode="[$-404]General"/>
     <numFmt numFmtId="171" formatCode="[$-404]ggge\年m\月d\日;@"/>
   </numFmts>
-  <fonts count="67">
+  <fonts count="68">
     <font>
       <name val="Noto Sans TC"/>
       <charset val="136"/>
@@ -524,6 +524,12 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="11.5"/>
+    </font>
+    <font>
+      <name val="標楷體"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="13">
@@ -600,7 +606,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -692,6 +698,27 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -703,7 +730,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1615,6 +1642,26 @@
     </xf>
     <xf numFmtId="171" fontId="41" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="67" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2012,25 +2059,23 @@
       <c r="F9" s="150" t="n"/>
       <c r="G9" s="150" t="n"/>
     </row>
-    <row r="10" ht="17.15" customHeight="1" s="148">
+    <row r="10" ht="38" customHeight="1" s="148">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>服務平台派選服務人員:</t>
         </is>
       </c>
       <c r="B10" s="166" t="n"/>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="312" t="inlineStr">
         <is>
           <t>服務人員(綁定好的服務人員)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="F10" s="313" t="inlineStr">
         <is>
           <t>服務 (以下簡稱受託人乙方)</t>
         </is>
       </c>
-      <c r="F10" s="166" t="n"/>
-      <c r="G10" s="150" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="148">
       <c r="A11" s="18" t="inlineStr">
@@ -2252,7 +2297,7 @@
       </c>
       <c r="D25" s="150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
@@ -2435,7 +2480,7 @@
       <c r="F33" s="205" t="n"/>
       <c r="G33" s="205" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="148">
+    <row r="34" ht="18" customHeight="1" s="148">
       <c r="A34" s="54" t="inlineStr">
         <is>
           <t>訂金</t>
@@ -2456,13 +2501,11 @@
           <t xml:space="preserve">雇主登記MAIL: </t>
         </is>
       </c>
-      <c r="E34" s="58" t="inlineStr">
+      <c r="E34" s="309" t="inlineStr">
         <is>
           <t>Email(市府表單)</t>
         </is>
       </c>
-      <c r="F34" s="211" t="n"/>
-      <c r="G34" s="211" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="148">
       <c r="A35" s="54" t="inlineStr">
@@ -2552,7 +2595,7 @@
       </c>
       <c r="C38" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D38" s="69" t="inlineStr">
@@ -4462,25 +4505,23 @@
       <c r="F180" s="291" t="n"/>
       <c r="G180" s="291" t="n"/>
     </row>
-    <row r="181" ht="15" customHeight="1" s="148">
+    <row r="181" ht="38" customHeight="1" s="148">
       <c r="A181" s="298" t="inlineStr">
         <is>
           <t>服務人員(乙方)：</t>
         </is>
       </c>
-      <c r="B181" s="141">
+      <c r="B181" s="310">
         <f>C10</f>
         <v/>
       </c>
-      <c r="C181" s="304" t="n"/>
-      <c r="D181" s="291" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (簽章)</t>
-        </is>
-      </c>
-      <c r="E181" s="291" t="n"/>
-      <c r="F181" s="291" t="n"/>
-      <c r="G181" s="291" t="n"/>
+      <c r="C181" s="314" t="n"/>
+      <c r="D181" s="314" t="n"/>
+      <c r="E181" s="315" t="inlineStr">
+        <is>
+          <t>（簽章）</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15" customHeight="1" s="148">
       <c r="A182" s="159" t="inlineStr">
@@ -4536,7 +4577,7 @@
       <c r="G185" s="150" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="116">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="C80:E80"/>
     <mergeCell ref="E40:G40"/>
@@ -4560,6 +4601,7 @@
     <mergeCell ref="C101:G101"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="A116:G116"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="C75:E75"/>
     <mergeCell ref="A131:G131"/>
     <mergeCell ref="A156:G156"/>
@@ -4580,14 +4622,18 @@
     <mergeCell ref="A168:G168"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E181:G181"/>
     <mergeCell ref="B95:C95"/>
     <mergeCell ref="C79:E79"/>
     <mergeCell ref="C73:E73"/>
     <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="C55:E55"/>
     <mergeCell ref="A106:G106"/>
+    <mergeCell ref="B181:D181"/>
     <mergeCell ref="C104:G104"/>
+    <mergeCell ref="E34:G34"/>
     <mergeCell ref="A147:G147"/>
     <mergeCell ref="A161:G161"/>
     <mergeCell ref="A26:F26"/>
@@ -4627,7 +4673,6 @@
     <mergeCell ref="C56:E56"/>
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="D95:E95"/>
-    <mergeCell ref="C10:D10"/>
     <mergeCell ref="C76:E76"/>
     <mergeCell ref="A114:G114"/>
     <mergeCell ref="C93:G93"/>

--- a/db/templates/contracts/contract_client_copy.xlsx
+++ b/db/templates/contracts/contract_client_copy.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="170" formatCode="[$-404]General"/>
     <numFmt numFmtId="171" formatCode="[$-404]ggge\年m\月d\日;@"/>
   </numFmts>
-  <fonts count="68">
+  <fonts count="69">
     <font>
       <name val="Noto Sans TC"/>
       <charset val="136"/>
@@ -527,6 +527,14 @@
     </font>
     <font>
       <name val="標楷體"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="標楷體"/>
+      <charset val="1"/>
+      <family val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
@@ -730,7 +738,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1661,6 +1669,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2027,7 +2038,7 @@
           <t>申請人甲方簽名:</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="316" t="inlineStr">
         <is>
           <t>客戶名稱(市府表單)</t>
         </is>

--- a/db/templates/contracts/contract_client_copy.xlsx
+++ b/db/templates/contracts/contract_client_copy.xlsx
@@ -2117,7 +2117,7 @@
     <row r="13" ht="15" customHeight="1" s="148">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>提供合法合規之照顧服務媒合與管理。"</t>
+          <t>提供合法合規之照顧服務媒合與管理。</t>
         </is>
       </c>
       <c r="B13" s="150" t="n"/>
@@ -2130,7 +2130,7 @@
     <row r="14" ht="15" customHeight="1" s="148">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>建立服務品質監督機制，包括隨機抽查與定期評估。"</t>
+          <t>建立服務品質監督機制，包括隨機抽查與定期評估。</t>
         </is>
       </c>
       <c r="B14" s="150" t="n"/>
@@ -2143,7 +2143,7 @@
     <row r="15" ht="15" customHeight="1" s="148">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>妥善保存並保護委託人及受照顧者之個人資料。"</t>
+          <t>妥善保存並保護委託人及受照顧者之個人資料。</t>
         </is>
       </c>
       <c r="B15" s="150" t="n"/>
@@ -2156,7 +2156,7 @@
     <row r="16" ht="15" customHeight="1" s="148">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>服務期間提供服務人員意外責任險。"</t>
+          <t>服務期間提供服務人員意外責任險。</t>
         </is>
       </c>
       <c r="B16" s="150" t="n"/>
@@ -2182,7 +2182,7 @@
     <row r="18" ht="15" customHeight="1" s="148">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>得因委託人或受照顧者違反契約而終止服務。"</t>
+          <t>得因委託人或受照顧者違反契約而終止服務。</t>
         </is>
       </c>
       <c r="B18" s="150" t="n"/>
@@ -2195,7 +2195,7 @@
     <row r="19" ht="15" customHeight="1" s="148">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>得依政府規範調整服務內容與流程。"</t>
+          <t>得依政府規範調整服務內容與流程。</t>
         </is>
       </c>
       <c r="B19" s="150" t="n"/>
@@ -2221,7 +2221,7 @@
     <row r="21" ht="15" customHeight="1" s="148">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>委託人如未滿二十歲且未結婚，應得其法定代理人之同意，契約方生效。"</t>
+          <t>委託人如未滿二十歲且未結婚，應得其法定代理人之同意，契約方生效。</t>
         </is>
       </c>
       <c r="B21" s="150" t="n"/>
